--- a/artfynd/A 26077-2024 artfynd.xlsx
+++ b/artfynd/A 26077-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>1547656</v>
       </c>
       <c r="B2" t="n">
-        <v>89411</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>716625.8507380376</v>
+        <v>716626</v>
       </c>
       <c r="R2" t="n">
-        <v>6394407.721269609</v>
+        <v>6394408</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,19 +752,9 @@
           <t>2008-02-28</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2008-02-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -814,15 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>83355364</v>
+        <v>83355356</v>
       </c>
       <c r="B3" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -858,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>716624.5183114847</v>
+        <v>716636</v>
       </c>
       <c r="R3" t="n">
-        <v>6394382.441285242</v>
+        <v>6394431</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -888,7 +868,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>676DC34F-55BE-4792-9017-5917473703E9</t>
+          <t>805C9515-A762-452C-8F1B-DAC9D4093480</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -896,19 +876,9 @@
           <t>2008-02-28</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2008-02-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -942,12 +912,7 @@
         <v>83355357</v>
       </c>
       <c r="B4" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>716639.0663551369</v>
+        <v>716639</v>
       </c>
       <c r="R4" t="n">
-        <v>6394421.838162858</v>
+        <v>6394422</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1021,19 +986,9 @@
           <t>2008-02-28</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2008-02-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1064,15 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>83355356</v>
+        <v>83355364</v>
       </c>
       <c r="B5" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>716635.8999459953</v>
+        <v>716625</v>
       </c>
       <c r="R5" t="n">
-        <v>6394430.786428683</v>
+        <v>6394382</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1138,7 +1088,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>805C9515-A762-452C-8F1B-DAC9D4093480</t>
+          <t>676DC34F-55BE-4792-9017-5917473703E9</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1146,19 +1096,9 @@
           <t>2008-02-28</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2008-02-28</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1182,6 +1122,336 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>83355366</v>
+      </c>
+      <c r="B6" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ask (Skyddsvärt träd), Gtl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>716618</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6394358</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bäl</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>F92319F9-5A2C-4126-BB8E-ECE90F3A1896</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2008-02-28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2008-02-28</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Oskar Kullingsjö</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Oskar Kullingsjö, Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>83355367</v>
+      </c>
+      <c r="B7" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ask (Skyddsvärt träd), Gtl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>716610</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6394340</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bäl</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>E807F531-2FAE-4375-B0BD-E693422FAB94</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2008-02-28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2008-02-28</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Oskar Kullingsjö</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Oskar Kullingsjö, Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>83355369</v>
+      </c>
+      <c r="B8" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ask (Skyddsvärt träd), Gtl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>716616</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6394339</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Bäl</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>FC8290A7-1DAD-4245-9FB8-92B791B7413F</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2008-02-28</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2008-02-28</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Oskar Kullingsjö</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Oskar Kullingsjö, Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
         <is>
           <t>Trädportalen</t>
         </is>

--- a/artfynd/A 26077-2024 artfynd.xlsx
+++ b/artfynd/A 26077-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -796,6 +801,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1547656</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,6 +916,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83355356</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1016,6 +1031,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83355357</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1126,6 +1146,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83355364</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1236,6 +1261,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83355366</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1346,6 +1376,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83355367</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1456,8 +1491,22 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83355369</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>